--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2753-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2753-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54E440E0-7B70-4EBF-B223-4B6E4DC8892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1BCE94E-008C-4403-90CB-BD92D6D0603F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{DF3CEE22-0894-4BC2-A93F-E6A0F89DEC1C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CFB14A49-030F-4334-A9AA-0E01E27CBC91}"/>
   </bookViews>
   <sheets>
     <sheet name="2753-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1496,25 +1496,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CDAB2C5-0B02-4788-B0EE-962E9DEFF82E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43892A8-BDA0-4C60-ABDE-24077634EFB1}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1542,7 +1542,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1668,7 +1668,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>3.38</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2166,7 +2166,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>3.82</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2664,7 +2664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>51</v>
       </c>
